--- a/Result/profitability/3094.xlsx
+++ b/Result/profitability/3094.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06125</v>
+        <v>0.1</v>
       </c>
       <c r="N2" t="n">
-        <v>70.70375</v>
+        <v>71.44624999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.11125</v>
       </c>
       <c r="N3" t="n">
-        <v>68.8175</v>
+        <v>69.97125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11</v>
+        <v>0.1425</v>
       </c>
       <c r="N4" t="n">
-        <v>67.08</v>
+        <v>66.24625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.12125</v>
+        <v>0.16625</v>
       </c>
       <c r="N5" t="n">
-        <v>64.14874999999999</v>
+        <v>63.93624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.165</v>
+        <v>0.18625</v>
       </c>
       <c r="N6" t="n">
-        <v>61.64375</v>
+        <v>62.07875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>0.185</v>
+        <v>0.215</v>
       </c>
       <c r="N7" t="n">
-        <v>60.2675</v>
+        <v>60.33875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.245</v>
+        <v>0.27625</v>
       </c>
       <c r="N8" t="n">
-        <v>58.64375</v>
+        <v>58.56999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.2925</v>
       </c>
       <c r="N9" t="n">
-        <v>57.65499999999999</v>
+        <v>57.655</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.415</v>
       </c>
       <c r="N12" t="n">
-        <v>63.04125</v>
+        <v>63.04125000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>64</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" t="n">
+        <v>47</v>
+      </c>
+      <c r="F75" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>29</v>
+      </c>
+      <c r="K75" t="n">
+        <v>27</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N75" t="n">
+        <v>73.1075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5900000000000034</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.007868765004001133</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.700000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0223419634643186</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
